--- a/excels/VFM_result_2026-05-30_02_04_17.xlsx
+++ b/excels/VFM_result_2026-05-30_02_04_17.xlsx
@@ -133,10 +133,10 @@
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-    <cellStyle name="5364472929231691707" xfId="1" hidden="0"/>
-    <cellStyle name="7500048928965369997" xfId="2" hidden="0"/>
-    <cellStyle name="-5377932276589313242" xfId="3" hidden="0"/>
-    <cellStyle name="-5796100613138199746" xfId="4" hidden="0"/>
+    <cellStyle name="-7760805106754422227" xfId="1" hidden="0"/>
+    <cellStyle name="165048512611222623" xfId="2" hidden="0"/>
+    <cellStyle name="6227448304050987142" xfId="3" hidden="0"/>
+    <cellStyle name="9020691385373205719" xfId="4" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
